--- a/output/all-profiles.xlsx
+++ b/output/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14774" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14774" uniqueCount="1121">
   <si>
     <t>Property</t>
   </si>
@@ -2193,6 +2193,10 @@
   </si>
   <si>
     <t>The quantity of vaccine product that was administered.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>Immunization.performer</t>
@@ -4802,7 +4806,7 @@
         <v>2</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="156">
@@ -4810,7 +4814,7 @@
         <v>4</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="157">
@@ -4826,7 +4830,7 @@
         <v>8</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="159">
@@ -4834,7 +4838,7 @@
         <v>10</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="160">
@@ -4858,7 +4862,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="163">
@@ -4890,7 +4894,7 @@
         <v>23</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="167">
@@ -4926,7 +4930,7 @@
         <v>31</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="172">
@@ -4934,7 +4938,7 @@
         <v>33</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="173">
@@ -32984,7 +32988,7 @@
         <v>75</v>
       </c>
       <c r="AK267" t="s" s="2">
-        <v>95</v>
+        <v>703</v>
       </c>
     </row>
     <row r="268">
@@ -32992,10 +32996,10 @@
         <v>508</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D268" s="2"/>
       <c r="E268" t="s" s="2">
@@ -33021,10 +33025,10 @@
         <v>350</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N268" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O268" s="2"/>
       <c r="P268" s="2"/>
@@ -33075,7 +33079,7 @@
         <v>75</v>
       </c>
       <c r="AG268" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AH268" t="s" s="2">
         <v>76</v>
@@ -33095,10 +33099,10 @@
         <v>508</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" t="s" s="2">
@@ -33198,10 +33202,10 @@
         <v>508</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" t="s" s="2">
@@ -33303,10 +33307,10 @@
         <v>508</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" t="s" s="2">
@@ -33410,10 +33414,10 @@
         <v>508</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" t="s" s="2">
@@ -33439,10 +33443,10 @@
         <v>145</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="O272" s="2"/>
       <c r="P272" s="2"/>
@@ -33473,7 +33477,7 @@
       </c>
       <c r="Z272" s="2"/>
       <c r="AA272" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AB272" t="s" s="2">
         <v>75</v>
@@ -33491,7 +33495,7 @@
         <v>75</v>
       </c>
       <c r="AG272" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AH272" t="s" s="2">
         <v>76</v>
@@ -33511,10 +33515,10 @@
         <v>508</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D273" s="2"/>
       <c r="E273" t="s" s="2">
@@ -33614,10 +33618,10 @@
         <v>508</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" t="s" s="2">
@@ -33719,10 +33723,10 @@
         <v>508</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" t="s" s="2">
@@ -33826,10 +33830,10 @@
         <v>508</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" t="s" s="2">
@@ -33929,10 +33933,10 @@
         <v>508</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" t="s" s="2">
@@ -34034,10 +34038,10 @@
         <v>508</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" t="s" s="2">
@@ -34141,10 +34145,10 @@
         <v>508</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" t="s" s="2">
@@ -34246,10 +34250,10 @@
         <v>508</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" t="s" s="2">
@@ -34351,10 +34355,10 @@
         <v>508</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" t="s" s="2">
@@ -34456,10 +34460,10 @@
         <v>508</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" t="s" s="2">
@@ -34563,10 +34567,10 @@
         <v>508</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" t="s" s="2">
@@ -34670,10 +34674,10 @@
         <v>508</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" t="s" s="2">
@@ -34696,16 +34700,16 @@
         <v>78</v>
       </c>
       <c r="L284" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M284" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N284" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O284" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P284" s="2"/>
       <c r="Q284" t="s" s="2">
@@ -34755,7 +34759,7 @@
         <v>75</v>
       </c>
       <c r="AG284" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AH284" t="s" s="2">
         <v>84</v>
@@ -34775,10 +34779,10 @@
         <v>508</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" t="s" s="2">
@@ -34878,10 +34882,10 @@
         <v>508</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
@@ -34983,10 +34987,10 @@
         <v>508</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
@@ -35088,10 +35092,10 @@
         <v>508</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
@@ -35193,10 +35197,10 @@
         <v>508</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
@@ -35298,10 +35302,10 @@
         <v>508</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" t="s" s="2">
@@ -35403,10 +35407,10 @@
         <v>508</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" t="s" s="2">
@@ -35432,10 +35436,10 @@
         <v>395</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N291" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O291" s="2"/>
       <c r="P291" s="2"/>
@@ -35486,7 +35490,7 @@
         <v>75</v>
       </c>
       <c r="AG291" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AH291" t="s" s="2">
         <v>76</v>
@@ -35506,10 +35510,10 @@
         <v>508</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
@@ -35535,10 +35539,10 @@
         <v>145</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N292" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O292" s="2"/>
       <c r="P292" s="2"/>
@@ -35568,10 +35572,10 @@
         <v>245</v>
       </c>
       <c r="Z292" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AA292" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AB292" t="s" s="2">
         <v>75</v>
@@ -35589,7 +35593,7 @@
         <v>75</v>
       </c>
       <c r="AG292" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AH292" t="s" s="2">
         <v>76</v>
@@ -35609,10 +35613,10 @@
         <v>508</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
@@ -35635,13 +35639,13 @@
         <v>75</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="O293" s="2"/>
       <c r="P293" s="2"/>
@@ -35692,7 +35696,7 @@
         <v>75</v>
       </c>
       <c r="AG293" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AH293" t="s" s="2">
         <v>76</v>
@@ -35712,10 +35716,10 @@
         <v>508</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
@@ -35741,20 +35745,20 @@
         <v>195</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N294" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O294" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="P294" s="2"/>
       <c r="Q294" t="s" s="2">
         <v>75</v>
       </c>
       <c r="R294" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="S294" t="s" s="2">
         <v>75</v>
@@ -35799,7 +35803,7 @@
         <v>75</v>
       </c>
       <c r="AG294" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AH294" t="s" s="2">
         <v>76</v>
@@ -35819,10 +35823,10 @@
         <v>508</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
@@ -35848,10 +35852,10 @@
         <v>145</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N295" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="O295" s="2"/>
       <c r="P295" s="2"/>
@@ -35881,10 +35885,10 @@
         <v>245</v>
       </c>
       <c r="Z295" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AA295" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AB295" t="s" s="2">
         <v>75</v>
@@ -35902,7 +35906,7 @@
         <v>75</v>
       </c>
       <c r="AG295" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AH295" t="s" s="2">
         <v>76</v>
@@ -35922,10 +35926,10 @@
         <v>508</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
@@ -35951,10 +35955,10 @@
         <v>350</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" s="2"/>
@@ -36005,7 +36009,7 @@
         <v>75</v>
       </c>
       <c r="AG296" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AH296" t="s" s="2">
         <v>76</v>
@@ -36017,7 +36021,7 @@
         <v>75</v>
       </c>
       <c r="AK296" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="297">
@@ -36025,10 +36029,10 @@
         <v>508</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" t="s" s="2">
@@ -36128,10 +36132,10 @@
         <v>508</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" t="s" s="2">
@@ -36233,10 +36237,10 @@
         <v>508</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" t="s" s="2">
@@ -36340,10 +36344,10 @@
         <v>508</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" t="s" s="2">
@@ -36369,10 +36373,10 @@
         <v>154</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="O300" s="2"/>
       <c r="P300" s="2"/>
@@ -36423,7 +36427,7 @@
         <v>75</v>
       </c>
       <c r="AG300" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AH300" t="s" s="2">
         <v>76</v>
@@ -36443,10 +36447,10 @@
         <v>508</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" t="s" s="2">
@@ -36472,10 +36476,10 @@
         <v>97</v>
       </c>
       <c r="M301" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N301" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O301" s="2"/>
       <c r="P301" s="2"/>
@@ -36526,7 +36530,7 @@
         <v>75</v>
       </c>
       <c r="AG301" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AH301" t="s" s="2">
         <v>76</v>
@@ -36546,10 +36550,10 @@
         <v>508</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" t="s" s="2">
@@ -36575,10 +36579,10 @@
         <v>329</v>
       </c>
       <c r="M302" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N302" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="O302" s="2"/>
       <c r="P302" s="2"/>
@@ -36629,7 +36633,7 @@
         <v>75</v>
       </c>
       <c r="AG302" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AH302" t="s" s="2">
         <v>76</v>
@@ -36649,10 +36653,10 @@
         <v>508</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" t="s" s="2">
@@ -36678,10 +36682,10 @@
         <v>329</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N303" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O303" s="2"/>
       <c r="P303" s="2"/>
@@ -36732,7 +36736,7 @@
         <v>75</v>
       </c>
       <c r="AG303" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AH303" t="s" s="2">
         <v>76</v>
@@ -36752,10 +36756,10 @@
         <v>508</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D304" s="2"/>
       <c r="E304" t="s" s="2">
@@ -36781,10 +36785,10 @@
         <v>145</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N304" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O304" s="2"/>
       <c r="P304" s="2"/>
@@ -36814,10 +36818,10 @@
         <v>245</v>
       </c>
       <c r="Z304" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA304" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AB304" t="s" s="2">
         <v>75</v>
@@ -36835,7 +36839,7 @@
         <v>75</v>
       </c>
       <c r="AG304" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AH304" t="s" s="2">
         <v>76</v>
@@ -36855,10 +36859,10 @@
         <v>508</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D305" s="2"/>
       <c r="E305" t="s" s="2">
@@ -36884,10 +36888,10 @@
         <v>145</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N305" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="O305" s="2"/>
       <c r="P305" s="2"/>
@@ -36917,10 +36921,10 @@
         <v>245</v>
       </c>
       <c r="Z305" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AA305" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AB305" t="s" s="2">
         <v>75</v>
@@ -36938,7 +36942,7 @@
         <v>75</v>
       </c>
       <c r="AG305" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>76</v>
@@ -36958,10 +36962,10 @@
         <v>508</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
@@ -36987,13 +36991,13 @@
         <v>350</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N306" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="O306" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P306" s="2"/>
       <c r="Q306" t="s" s="2">
@@ -37043,7 +37047,7 @@
         <v>75</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AH306" t="s" s="2">
         <v>76</v>
@@ -37063,10 +37067,10 @@
         <v>508</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
@@ -37166,10 +37170,10 @@
         <v>508</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D308" s="2"/>
       <c r="E308" t="s" s="2">
@@ -37271,10 +37275,10 @@
         <v>508</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
@@ -37378,10 +37382,10 @@
         <v>508</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
@@ -37407,10 +37411,10 @@
         <v>329</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N310" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="O310" s="2"/>
       <c r="P310" s="2"/>
@@ -37461,7 +37465,7 @@
         <v>75</v>
       </c>
       <c r="AG310" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AH310" t="s" s="2">
         <v>76</v>
@@ -37481,10 +37485,10 @@
         <v>508</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -37507,13 +37511,13 @@
         <v>75</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N311" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="O311" s="2"/>
       <c r="P311" s="2"/>
@@ -37564,7 +37568,7 @@
         <v>75</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AH311" t="s" s="2">
         <v>76</v>
@@ -37584,10 +37588,10 @@
         <v>508</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
@@ -37613,10 +37617,10 @@
         <v>195</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="O312" s="2"/>
       <c r="P312" s="2"/>
@@ -37667,7 +37671,7 @@
         <v>75</v>
       </c>
       <c r="AG312" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AH312" t="s" s="2">
         <v>76</v>
@@ -37687,10 +37691,10 @@
         <v>508</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -37716,10 +37720,10 @@
         <v>350</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="O313" s="2"/>
       <c r="P313" s="2"/>
@@ -37770,7 +37774,7 @@
         <v>75</v>
       </c>
       <c r="AG313" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AH313" t="s" s="2">
         <v>76</v>
@@ -37790,10 +37794,10 @@
         <v>508</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -37893,10 +37897,10 @@
         <v>508</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -37994,13 +37998,13 @@
         <v>508</v>
       </c>
       <c r="B316" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="C316" t="s" s="2">
         <v>808</v>
       </c>
-      <c r="C316" t="s" s="2">
-        <v>807</v>
-      </c>
       <c r="D316" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E316" t="s" s="2">
         <v>75</v>
@@ -38022,13 +38026,13 @@
         <v>75</v>
       </c>
       <c r="L316" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M316" t="s" s="2">
         <v>458</v>
       </c>
       <c r="N316" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="O316" s="2"/>
       <c r="P316" s="2"/>
@@ -38099,13 +38103,13 @@
         <v>508</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D317" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E317" t="s" s="2">
         <v>469</v>
@@ -38127,13 +38131,13 @@
         <v>75</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O317" s="2"/>
       <c r="P317" s="2"/>
@@ -38204,10 +38208,10 @@
         <v>508</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -38307,10 +38311,10 @@
         <v>508</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -38410,10 +38414,10 @@
         <v>508</v>
       </c>
       <c r="B320" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="C320" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="C320" t="s" s="2">
-        <v>820</v>
       </c>
       <c r="D320" t="s" s="2">
         <v>472</v>
@@ -38443,10 +38447,10 @@
         <v>127</v>
       </c>
       <c r="M320" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N320" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="O320" s="2"/>
       <c r="P320" s="2"/>
@@ -38517,10 +38521,10 @@
         <v>508</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -38620,10 +38624,10 @@
         <v>508</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
@@ -38725,10 +38729,10 @@
         <v>508</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
@@ -38830,10 +38834,10 @@
         <v>508</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -38933,10 +38937,10 @@
         <v>508</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D325" t="s" s="2">
         <v>484</v>
@@ -38966,10 +38970,10 @@
         <v>127</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N325" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O325" s="2"/>
       <c r="P325" s="2"/>
@@ -39040,10 +39044,10 @@
         <v>508</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -39143,10 +39147,10 @@
         <v>508</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -39248,10 +39252,10 @@
         <v>508</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -39353,10 +39357,10 @@
         <v>508</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -39456,10 +39460,10 @@
         <v>508</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D330" t="s" s="2">
         <v>492</v>
@@ -39489,10 +39493,10 @@
         <v>127</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="O330" s="2"/>
       <c r="P330" s="2"/>
@@ -39563,10 +39567,10 @@
         <v>508</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -39666,10 +39670,10 @@
         <v>508</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -39771,10 +39775,10 @@
         <v>508</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -39876,10 +39880,10 @@
         <v>508</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -39979,10 +39983,10 @@
         <v>508</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -40084,10 +40088,10 @@
         <v>508</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -40187,10 +40191,10 @@
         <v>508</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -40294,10 +40298,10 @@
         <v>508</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -40323,10 +40327,10 @@
         <v>154</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="N338" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="O338" s="2"/>
       <c r="P338" s="2"/>
@@ -40377,7 +40381,7 @@
         <v>75</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>76</v>
@@ -40397,10 +40401,10 @@
         <v>508</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -40426,10 +40430,10 @@
         <v>313</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="O339" s="2"/>
       <c r="P339" s="2"/>
@@ -40480,7 +40484,7 @@
         <v>75</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>76</v>
@@ -40500,10 +40504,10 @@
         <v>508</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -40529,10 +40533,10 @@
         <v>145</v>
       </c>
       <c r="M340" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="N340" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="O340" s="2"/>
       <c r="P340" s="2"/>
@@ -40562,10 +40566,10 @@
         <v>245</v>
       </c>
       <c r="Z340" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AA340" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AB340" t="s" s="2">
         <v>75</v>
@@ -40583,7 +40587,7 @@
         <v>75</v>
       </c>
       <c r="AG340" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AH340" t="s" s="2">
         <v>76</v>
@@ -40603,10 +40607,10 @@
         <v>508</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -40632,13 +40636,13 @@
         <v>154</v>
       </c>
       <c r="M341" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N341" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="O341" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="P341" s="2"/>
       <c r="Q341" t="s" s="2">
@@ -40667,10 +40671,10 @@
         <v>149</v>
       </c>
       <c r="Z341" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AA341" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AB341" t="s" s="2">
         <v>75</v>
@@ -40688,7 +40692,7 @@
         <v>75</v>
       </c>
       <c r="AG341" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AH341" t="s" s="2">
         <v>84</v>
@@ -40708,10 +40712,10 @@
         <v>508</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
@@ -40734,16 +40738,16 @@
         <v>75</v>
       </c>
       <c r="L342" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N342" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="O342" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="P342" s="2"/>
       <c r="Q342" t="s" s="2">
@@ -40793,7 +40797,7 @@
         <v>75</v>
       </c>
       <c r="AG342" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AH342" t="s" s="2">
         <v>76</v>
@@ -40810,17 +40814,17 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F343" s="2"/>
       <c r="G343" t="s" s="2">
@@ -40842,13 +40846,13 @@
         <v>79</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="O343" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="P343" s="2"/>
       <c r="Q343" t="s" s="2">
@@ -40898,7 +40902,7 @@
         <v>75</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>76</v>
@@ -40915,13 +40919,13 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -41020,13 +41024,13 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -41123,13 +41127,13 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -41228,13 +41232,13 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -41333,13 +41337,13 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
@@ -41438,13 +41442,13 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -41543,13 +41547,13 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -41648,13 +41652,13 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -41755,13 +41759,13 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -41787,13 +41791,13 @@
         <v>139</v>
       </c>
       <c r="M352" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="N352" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="O352" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="P352" s="2"/>
       <c r="Q352" t="s" s="2">
@@ -41843,7 +41847,7 @@
         <v>75</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AH352" t="s" s="2">
         <v>76</v>
@@ -41860,13 +41864,13 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -41892,16 +41896,16 @@
         <v>103</v>
       </c>
       <c r="M353" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="N353" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="O353" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="P353" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="Q353" t="s" s="2">
         <v>75</v>
@@ -41929,10 +41933,10 @@
         <v>149</v>
       </c>
       <c r="Z353" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AA353" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="AB353" t="s" s="2">
         <v>75</v>
@@ -41950,7 +41954,7 @@
         <v>75</v>
       </c>
       <c r="AG353" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>84</v>
@@ -41967,13 +41971,13 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" t="s" s="2">
@@ -41999,16 +42003,16 @@
         <v>145</v>
       </c>
       <c r="M354" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="N354" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="O354" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="P354" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="Q354" t="s" s="2">
         <v>75</v>
@@ -42036,28 +42040,28 @@
         <v>149</v>
       </c>
       <c r="Z354" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="AA354" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="AB354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF354" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG354" t="s" s="2">
         <v>904</v>
-      </c>
-      <c r="AA354" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="AB354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF354" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG354" t="s" s="2">
-        <v>903</v>
       </c>
       <c r="AH354" t="s" s="2">
         <v>84</v>
@@ -42074,13 +42078,13 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -42177,13 +42181,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -42282,13 +42286,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -42389,13 +42393,13 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
@@ -42496,13 +42500,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -42528,16 +42532,16 @@
         <v>145</v>
       </c>
       <c r="M359" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="N359" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="O359" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="P359" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="Q359" t="s" s="2">
         <v>75</v>
@@ -42565,10 +42569,10 @@
         <v>245</v>
       </c>
       <c r="Z359" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="AA359" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AB359" t="s" s="2">
         <v>75</v>
@@ -42586,7 +42590,7 @@
         <v>75</v>
       </c>
       <c r="AG359" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AH359" t="s" s="2">
         <v>76</v>
@@ -42603,13 +42607,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -42706,13 +42710,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -42811,13 +42815,13 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -42918,13 +42922,13 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -43025,13 +43029,13 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
@@ -43057,16 +43061,16 @@
         <v>250</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="O364" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="P364" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="Q364" t="s" s="2">
         <v>75</v>
@@ -43115,7 +43119,7 @@
         <v>75</v>
       </c>
       <c r="AG364" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AH364" t="s" s="2">
         <v>76</v>
@@ -43132,13 +43136,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -43235,13 +43239,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -43340,13 +43344,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -43445,13 +43449,13 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -43550,13 +43554,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -43582,10 +43586,10 @@
         <v>139</v>
       </c>
       <c r="M369" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="N369" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="O369" t="s" s="2">
         <v>274</v>
@@ -43655,13 +43659,13 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -43758,13 +43762,13 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -43863,13 +43867,13 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -43970,13 +43974,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -44077,13 +44081,13 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -44184,13 +44188,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -44289,13 +44293,13 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -44392,13 +44396,13 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -44497,13 +44501,13 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -44602,13 +44606,13 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -44634,14 +44638,14 @@
         <v>324</v>
       </c>
       <c r="M379" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="N379" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="O379" s="2"/>
       <c r="P379" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="Q379" t="s" s="2">
         <v>75</v>
@@ -44690,7 +44694,7 @@
         <v>75</v>
       </c>
       <c r="AG379" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AH379" t="s" s="2">
         <v>76</v>
@@ -44707,13 +44711,13 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -44739,16 +44743,16 @@
         <v>329</v>
       </c>
       <c r="M380" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="N380" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="O380" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="P380" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="Q380" t="s" s="2">
         <v>75</v>
@@ -44797,7 +44801,7 @@
         <v>75</v>
       </c>
       <c r="AG380" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AH380" t="s" s="2">
         <v>84</v>
@@ -44814,13 +44818,13 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -44843,17 +44847,17 @@
         <v>78</v>
       </c>
       <c r="L381" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M381" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="N381" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="O381" s="2"/>
       <c r="P381" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="Q381" t="s" s="2">
         <v>75</v>
@@ -44902,7 +44906,7 @@
         <v>75</v>
       </c>
       <c r="AG381" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AH381" t="s" s="2">
         <v>84</v>
@@ -44919,13 +44923,13 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
@@ -45022,13 +45026,13 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -45127,13 +45131,13 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -45232,13 +45236,13 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -45337,13 +45341,13 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
@@ -45369,7 +45373,7 @@
         <v>139</v>
       </c>
       <c r="M386" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="N386" t="s" s="2">
         <v>273</v>
@@ -45442,13 +45446,13 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -45545,13 +45549,13 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
@@ -45650,13 +45654,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -45757,13 +45761,13 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D390" s="2"/>
       <c r="E390" t="s" s="2">
@@ -45864,13 +45868,13 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D391" s="2"/>
       <c r="E391" t="s" s="2">
@@ -45971,13 +45975,13 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D392" s="2"/>
       <c r="E392" t="s" s="2">
@@ -46076,13 +46080,13 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D393" s="2"/>
       <c r="E393" t="s" s="2">
@@ -46179,13 +46183,13 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D394" s="2"/>
       <c r="E394" t="s" s="2">
@@ -46284,13 +46288,13 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
@@ -46389,13 +46393,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
@@ -46421,13 +46425,13 @@
         <v>154</v>
       </c>
       <c r="M396" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="N396" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="O396" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="P396" s="2"/>
       <c r="Q396" t="s" s="2">
@@ -46435,7 +46439,7 @@
       </c>
       <c r="R396" s="2"/>
       <c r="S396" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="T396" t="s" s="2">
         <v>75</v>
@@ -46477,7 +46481,7 @@
         <v>75</v>
       </c>
       <c r="AG396" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AH396" t="s" s="2">
         <v>84</v>
@@ -46494,13 +46498,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D397" s="2"/>
       <c r="E397" t="s" s="2">
@@ -46526,13 +46530,13 @@
         <v>103</v>
       </c>
       <c r="M397" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="N397" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="O397" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="P397" s="2"/>
       <c r="Q397" t="s" s="2">
@@ -46561,10 +46565,10 @@
         <v>149</v>
       </c>
       <c r="Z397" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="AA397" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AB397" t="s" s="2">
         <v>75</v>
@@ -46582,7 +46586,7 @@
         <v>75</v>
       </c>
       <c r="AG397" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="AH397" t="s" s="2">
         <v>76</v>
@@ -46599,13 +46603,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D398" s="2"/>
       <c r="E398" t="s" s="2">
@@ -46631,16 +46635,16 @@
         <v>350</v>
       </c>
       <c r="M398" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="N398" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="O398" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="P398" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="Q398" t="s" s="2">
         <v>75</v>
@@ -46689,7 +46693,7 @@
         <v>75</v>
       </c>
       <c r="AG398" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="AH398" t="s" s="2">
         <v>76</v>
@@ -46706,13 +46710,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D399" s="2"/>
       <c r="E399" t="s" s="2">
@@ -46809,13 +46813,13 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" t="s" s="2">
@@ -46914,13 +46918,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D401" s="2"/>
       <c r="E401" t="s" s="2">
@@ -47021,13 +47025,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" t="s" s="2">
@@ -47053,14 +47057,14 @@
         <v>103</v>
       </c>
       <c r="M402" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="N402" t="s" s="2">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="O402" s="2"/>
       <c r="P402" t="s" s="2">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="Q402" t="s" s="2">
         <v>75</v>
@@ -47088,10 +47092,10 @@
         <v>149</v>
       </c>
       <c r="Z402" t="s" s="2">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="AA402" t="s" s="2">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="AB402" t="s" s="2">
         <v>75</v>
@@ -47109,7 +47113,7 @@
         <v>75</v>
       </c>
       <c r="AG402" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AH402" t="s" s="2">
         <v>84</v>
@@ -47126,13 +47130,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D403" s="2"/>
       <c r="E403" t="s" s="2">
@@ -47158,14 +47162,14 @@
         <v>329</v>
       </c>
       <c r="M403" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="N403" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="O403" s="2"/>
       <c r="P403" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="Q403" t="s" s="2">
         <v>75</v>
@@ -47214,7 +47218,7 @@
         <v>75</v>
       </c>
       <c r="AG403" t="s" s="2">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="AH403" t="s" s="2">
         <v>76</v>
@@ -47231,13 +47235,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" t="s" s="2">
@@ -47260,17 +47264,17 @@
         <v>75</v>
       </c>
       <c r="L404" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M404" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="N404" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="O404" s="2"/>
       <c r="P404" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="Q404" t="s" s="2">
         <v>75</v>
@@ -47319,7 +47323,7 @@
         <v>75</v>
       </c>
       <c r="AG404" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="AH404" t="s" s="2">
         <v>76</v>
@@ -47336,13 +47340,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -47368,16 +47372,16 @@
         <v>313</v>
       </c>
       <c r="M405" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="N405" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="O405" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="P405" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="Q405" t="s" s="2">
         <v>75</v>
@@ -47426,7 +47430,7 @@
         <v>75</v>
       </c>
       <c r="AG405" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="AH405" t="s" s="2">
         <v>76</v>
@@ -47443,13 +47447,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D406" s="2"/>
       <c r="E406" t="s" s="2">
@@ -47475,13 +47479,13 @@
         <v>350</v>
       </c>
       <c r="M406" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="N406" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="O406" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="P406" s="2"/>
       <c r="Q406" t="s" s="2">
@@ -47531,7 +47535,7 @@
         <v>75</v>
       </c>
       <c r="AG406" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="AH406" t="s" s="2">
         <v>76</v>
@@ -47548,13 +47552,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -47651,13 +47655,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D408" s="2"/>
       <c r="E408" t="s" s="2">
@@ -47756,13 +47760,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D409" s="2"/>
       <c r="E409" t="s" s="2">
@@ -47863,13 +47867,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" t="s" s="2">
@@ -47895,13 +47899,13 @@
         <v>103</v>
       </c>
       <c r="M410" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="N410" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="O410" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="P410" s="2"/>
       <c r="Q410" t="s" s="2">
@@ -47930,10 +47934,10 @@
         <v>149</v>
       </c>
       <c r="Z410" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="AA410" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="AB410" t="s" s="2">
         <v>75</v>
@@ -47951,7 +47955,7 @@
         <v>75</v>
       </c>
       <c r="AG410" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AH410" t="s" s="2">
         <v>84</v>
@@ -47968,13 +47972,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" t="s" s="2">
@@ -47997,13 +48001,13 @@
         <v>75</v>
       </c>
       <c r="L411" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M411" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="N411" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="O411" s="2"/>
       <c r="P411" s="2"/>
@@ -48054,7 +48058,7 @@
         <v>75</v>
       </c>
       <c r="AG411" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AH411" t="s" s="2">
         <v>84</v>
@@ -48071,13 +48075,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" t="s" s="2">
@@ -48103,16 +48107,16 @@
         <v>350</v>
       </c>
       <c r="M412" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="N412" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="O412" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="P412" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="Q412" t="s" s="2">
         <v>75</v>
@@ -48161,7 +48165,7 @@
         <v>75</v>
       </c>
       <c r="AG412" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AH412" t="s" s="2">
         <v>76</v>
@@ -48178,13 +48182,13 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D413" s="2"/>
       <c r="E413" t="s" s="2">
@@ -48281,13 +48285,13 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" t="s" s="2">
@@ -48386,13 +48390,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -48493,13 +48497,13 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -48525,13 +48529,13 @@
         <v>145</v>
       </c>
       <c r="M416" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N416" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O416" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="P416" s="2"/>
       <c r="Q416" t="s" s="2">
@@ -48560,10 +48564,10 @@
         <v>245</v>
       </c>
       <c r="Z416" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AA416" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="AB416" t="s" s="2">
         <v>75</v>
@@ -48581,7 +48585,7 @@
         <v>75</v>
       </c>
       <c r="AG416" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="AH416" t="s" s="2">
         <v>76</v>
@@ -48598,13 +48602,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" t="s" s="2">
@@ -48630,10 +48634,10 @@
         <v>308</v>
       </c>
       <c r="M417" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="N417" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="O417" s="2"/>
       <c r="P417" s="2"/>
@@ -48684,7 +48688,7 @@
         <v>75</v>
       </c>
       <c r="AG417" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="AH417" t="s" s="2">
         <v>76</v>
@@ -48701,13 +48705,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -48733,10 +48737,10 @@
         <v>391</v>
       </c>
       <c r="M418" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N418" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="O418" s="2"/>
       <c r="P418" s="2"/>
@@ -48787,7 +48791,7 @@
         <v>75</v>
       </c>
       <c r="AG418" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="AH418" t="s" s="2">
         <v>76</v>
@@ -48804,13 +48808,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -48836,10 +48840,10 @@
         <v>350</v>
       </c>
       <c r="M419" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="N419" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="O419" s="2"/>
       <c r="P419" s="2"/>
@@ -48890,7 +48894,7 @@
         <v>75</v>
       </c>
       <c r="AG419" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="AH419" t="s" s="2">
         <v>76</v>
@@ -48902,18 +48906,18 @@
         <v>75</v>
       </c>
       <c r="AK419" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -49010,13 +49014,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" t="s" s="2">
@@ -49115,13 +49119,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -49222,17 +49226,17 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F423" s="2"/>
       <c r="G423" t="s" s="2">
@@ -49254,16 +49258,16 @@
         <v>154</v>
       </c>
       <c r="M423" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="N423" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="O423" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="P423" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="Q423" t="s" s="2">
         <v>75</v>
@@ -49312,7 +49316,7 @@
         <v>75</v>
       </c>
       <c r="AG423" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AH423" t="s" s="2">
         <v>76</v>
@@ -49329,13 +49333,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" t="s" s="2">
@@ -49361,16 +49365,16 @@
         <v>145</v>
       </c>
       <c r="M424" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N424" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="O424" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="P424" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="Q424" t="s" s="2">
         <v>75</v>
@@ -49398,10 +49402,10 @@
         <v>245</v>
       </c>
       <c r="Z424" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AA424" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AB424" t="s" s="2">
         <v>75</v>
@@ -49419,7 +49423,7 @@
         <v>75</v>
       </c>
       <c r="AG424" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="AH424" t="s" s="2">
         <v>76</v>
@@ -49436,13 +49440,13 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D425" s="2"/>
       <c r="E425" t="s" s="2">
@@ -49465,17 +49469,17 @@
         <v>75</v>
       </c>
       <c r="L425" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="M425" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="N425" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="O425" s="2"/>
       <c r="P425" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="Q425" t="s" s="2">
         <v>75</v>
@@ -49524,7 +49528,7 @@
         <v>75</v>
       </c>
       <c r="AG425" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="AH425" t="s" s="2">
         <v>76</v>
@@ -49541,13 +49545,13 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D426" s="2"/>
       <c r="E426" t="s" s="2">
@@ -49573,13 +49577,13 @@
         <v>391</v>
       </c>
       <c r="M426" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="N426" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="O426" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="P426" s="2"/>
       <c r="Q426" t="s" s="2">
@@ -49629,7 +49633,7 @@
         <v>75</v>
       </c>
       <c r="AG426" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AH426" t="s" s="2">
         <v>76</v>
@@ -49646,13 +49650,13 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D427" s="2"/>
       <c r="E427" t="s" s="2">
@@ -49678,13 +49682,13 @@
         <v>113</v>
       </c>
       <c r="M427" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N427" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="O427" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="P427" s="2"/>
       <c r="Q427" t="s" s="2">
@@ -49734,7 +49738,7 @@
         <v>75</v>
       </c>
       <c r="AG427" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="AH427" t="s" s="2">
         <v>76</v>
@@ -49743,7 +49747,7 @@
         <v>84</v>
       </c>
       <c r="AJ427" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AK427" t="s" s="2">
         <v>95</v>
@@ -49751,13 +49755,13 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" t="s" s="2">
@@ -49783,16 +49787,16 @@
         <v>103</v>
       </c>
       <c r="M428" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="N428" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="O428" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="P428" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="Q428" t="s" s="2">
         <v>75</v>
@@ -49820,10 +49824,10 @@
         <v>149</v>
       </c>
       <c r="Z428" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="AA428" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AB428" t="s" s="2">
         <v>75</v>
@@ -49841,7 +49845,7 @@
         <v>75</v>
       </c>
       <c r="AG428" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="AH428" t="s" s="2">
         <v>76</v>
@@ -49858,13 +49862,13 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" t="s" s="2">
@@ -49890,16 +49894,16 @@
         <v>145</v>
       </c>
       <c r="M429" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="N429" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="O429" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="P429" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="Q429" t="s" s="2">
         <v>75</v>
@@ -49927,10 +49931,10 @@
         <v>107</v>
       </c>
       <c r="Z429" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AA429" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AB429" t="s" s="2">
         <v>75</v>
@@ -49948,7 +49952,7 @@
         <v>75</v>
       </c>
       <c r="AG429" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AH429" t="s" s="2">
         <v>76</v>
@@ -49965,13 +49969,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" t="s" s="2">
@@ -49994,16 +49998,16 @@
         <v>75</v>
       </c>
       <c r="L430" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="M430" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="N430" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="O430" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="P430" s="2"/>
       <c r="Q430" t="s" s="2">
@@ -50053,7 +50057,7 @@
         <v>75</v>
       </c>
       <c r="AG430" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="AH430" t="s" s="2">
         <v>76</v>
@@ -50062,7 +50066,7 @@
         <v>77</v>
       </c>
       <c r="AJ430" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="AK430" t="s" s="2">
         <v>95</v>
@@ -50070,13 +50074,13 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" t="s" s="2">
@@ -50173,13 +50177,13 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" t="s" s="2">
@@ -50278,13 +50282,13 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" t="s" s="2">
@@ -50383,13 +50387,13 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D434" s="2"/>
       <c r="E434" t="s" s="2">
@@ -50488,13 +50492,13 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D435" s="2"/>
       <c r="E435" t="s" s="2">
@@ -50593,13 +50597,13 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D436" s="2"/>
       <c r="E436" t="s" s="2">
@@ -50698,13 +50702,13 @@
     </row>
     <row r="437">
       <c r="A437" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D437" s="2"/>
       <c r="E437" t="s" s="2">
@@ -50730,16 +50734,16 @@
         <v>145</v>
       </c>
       <c r="M437" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="N437" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="O437" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="P437" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="Q437" t="s" s="2">
         <v>75</v>
@@ -50767,10 +50771,10 @@
         <v>107</v>
       </c>
       <c r="Z437" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="AA437" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="AB437" t="s" s="2">
         <v>75</v>
@@ -50788,7 +50792,7 @@
         <v>75</v>
       </c>
       <c r="AG437" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AH437" t="s" s="2">
         <v>76</v>
@@ -50797,7 +50801,7 @@
         <v>84</v>
       </c>
       <c r="AJ437" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="AK437" t="s" s="2">
         <v>95</v>
@@ -50805,13 +50809,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D438" s="2"/>
       <c r="E438" t="s" s="2">
@@ -50837,13 +50841,13 @@
         <v>75</v>
       </c>
       <c r="M438" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="N438" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="O438" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="P438" s="2"/>
       <c r="Q438" t="s" s="2">
@@ -50893,7 +50897,7 @@
         <v>75</v>
       </c>
       <c r="AG438" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="AH438" t="s" s="2">
         <v>76</v>
@@ -50902,7 +50906,7 @@
         <v>77</v>
       </c>
       <c r="AJ438" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="AK438" t="s" s="2">
         <v>95</v>
